--- a/backend/sample_programs.xlsx
+++ b/backend/sample_programs.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -463,13 +463,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BTECH-EE</v>
+        <v>BTECH-CE</v>
       </c>
       <c r="B5" t="str">
-        <v>Bachelor of Technology in Electrical Engineering</v>
+        <v>Bachelor of Technology in Civil Engineering</v>
       </c>
       <c r="C5" t="str">
-        <v>EE</v>
+        <v>CE</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -477,13 +477,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BTECH-CE</v>
+        <v>BTECH-EE</v>
       </c>
       <c r="B6" t="str">
-        <v>Bachelor of Technology in Civil Engineering</v>
+        <v>Bachelor of Technology in Electrical Engineering</v>
       </c>
       <c r="C6" t="str">
-        <v>CE</v>
+        <v>EE</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -491,63 +491,49 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MCA</v>
+        <v>BTECH-AI</v>
       </c>
       <c r="B7" t="str">
-        <v>Master of Computer Applications</v>
+        <v>Bachelor of Technology in AI and Data Science</v>
       </c>
       <c r="C7" t="str">
-        <v>CA</v>
+        <v>AI</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MCAI</v>
+        <v>MCA</v>
       </c>
       <c r="B8" t="str">
-        <v>Integrated Master of Computer Applications</v>
+        <v>Master of Computer Applications</v>
       </c>
       <c r="C8" t="str">
         <v>CA</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MTECH-CS</v>
+        <v>MCAI</v>
       </c>
       <c r="B9" t="str">
-        <v>Master of Technology in Computer Science</v>
+        <v>Integrated Master of Computer Applications</v>
       </c>
       <c r="C9" t="str">
-        <v>CS</v>
+        <v>CA</v>
       </c>
       <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>MTECH-ME</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Master of Technology in Mechanical Engineering</v>
-      </c>
-      <c r="C10" t="str">
-        <v>ME</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>